--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487576_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487576_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9453</v>
+        <v>4.7236</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3484</v>
+        <v>5.7148</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4032</v>
+        <v>-0.9912</v>
       </c>
       <c r="G2" t="n">
         <v>-0.2993</v>
@@ -610,13 +610,13 @@
         <v>2.1543</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1942</v>
+        <v>0.9725</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0018</v>
+        <v>0.3646</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1959</v>
+        <v>0.6078</v>
       </c>
       <c r="V2" t="n">
         <v>3.8546</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4356</v>
+        <v>1.1527</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1338</v>
+        <v>2.3745</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3019</v>
+        <v>-1.2218</v>
       </c>
       <c r="G3" t="n">
         <v>1.4638</v>
@@ -688,13 +688,13 @@
         <v>2.1543</v>
       </c>
       <c r="S3" t="n">
-        <v>3.0941</v>
+        <v>0.8112</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7399</v>
+        <v>-0.0194</v>
       </c>
       <c r="U3" t="n">
-        <v>2.3543</v>
+        <v>0.8306</v>
       </c>
       <c r="V3" t="n">
         <v>0.6403</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.613</v>
+        <v>1.0061</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3724</v>
+        <v>1.7388</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7594</v>
+        <v>-0.7326</v>
       </c>
       <c r="G4" t="n">
         <v>0.4512</v>
@@ -766,13 +766,13 @@
         <v>1.1751</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0419</v>
+        <v>0.4351</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0288</v>
+        <v>0.3952</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0131</v>
+        <v>0.0399</v>
       </c>
       <c r="V4" t="n">
         <v>1.8825</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. RODRÍGUEZ DÍEZ</t>
+          <t>Y. IGLESIAS MENDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.7361</v>
+        <v>-0.4432</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0376</v>
+        <v>0.9683</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6985</v>
+        <v>-1.4116</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7302</v>
+        <v>-0.4381</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5029</v>
+        <v>-2.1307</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2273</v>
+        <v>1.6926</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08119999999999999</v>
+        <v>2.715</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0408</v>
+        <v>-1.2505</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0404</v>
+        <v>3.9655</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8114</v>
+        <v>-3.153</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5437</v>
+        <v>-0.8801</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2677</v>
+        <v>-2.2729</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1958</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1958</v>
+        <v>1.3709</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2018</v>
+        <v>-0.1156</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1188</v>
+        <v>-0.0635</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.083</v>
+        <v>-0.052</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.6979</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.4226</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. NONGO N'SALA</t>
+          <t>H. RODRÍGUEZ DÍEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9495</v>
+        <v>-0.4512</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0618</v>
+        <v>0.1671</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0113</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5496</v>
+        <v>-0.7302</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1354</v>
+        <v>-0.5029</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4142</v>
+        <v>-0.2273</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1212</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.0408</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1212</v>
+        <v>0.0404</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6708</v>
+        <v>-0.8114</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1354</v>
+        <v>-0.5437</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5354</v>
+        <v>-0.2677</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.1958</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.1958</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1246</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0594</v>
+        <v>0.0859</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.0028</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. SALVADORES ALVAREZ</t>
+          <t>A. NONGO N'SALA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0083</v>
+        <v>-0.7402</v>
       </c>
       <c r="E7" t="n">
-        <v>0.948</v>
+        <v>0.1642</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.9563</v>
+        <v>-0.9044</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1235</v>
+        <v>-0.5496</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.1898</v>
+        <v>-0.1354</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0664</v>
+        <v>-0.4142</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1577</v>
+        <v>0.1212</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.242</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3.3997</v>
+        <v>0.1212</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.2812</v>
+        <v>-0.6708</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9479</v>
+        <v>-0.1354</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.3333</v>
+        <v>-0.5354</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3917</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5668</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2498</v>
+        <v>0.0847</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4734</v>
+        <v>0.0429</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7233000000000001</v>
+        <v>0.0418</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2433</v>
+        <v>-0.2754</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5187</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Y. IGLESIAS MENDEZ</t>
+          <t>F. SALVADORES ALVAREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.236</v>
+        <v>-1.0864</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7637</v>
+        <v>0.4957</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.9996</v>
+        <v>-1.5821</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4381</v>
+        <v>-0.1235</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.1307</v>
+        <v>-2.1898</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6926</v>
+        <v>2.0664</v>
       </c>
       <c r="J8" t="n">
-        <v>2.715</v>
+        <v>2.1577</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.2505</v>
+        <v>-1.242</v>
       </c>
       <c r="L8" t="n">
-        <v>3.9655</v>
+        <v>3.3997</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.153</v>
+        <v>-2.2812</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8801</v>
+        <v>-0.9479</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.2729</v>
+        <v>-1.3333</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.5875</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3709</v>
+        <v>1.5668</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9083</v>
+        <v>-0.3279</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2682</v>
+        <v>0.0212</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6401</v>
+        <v>-0.3491</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6979</v>
+        <v>-0.2433</v>
       </c>
       <c r="W8" t="n">
         <v>0.2754</v>
       </c>
       <c r="X8" t="n">
-        <v>0.4226</v>
+        <v>-0.5187</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3753</v>
+        <v>-1.5975</v>
       </c>
       <c r="E9" t="n">
-        <v>1.153</v>
+        <v>0.7437</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.5283</v>
+        <v>-2.3412</v>
       </c>
       <c r="G9" t="n">
         <v>-1.681</v>
@@ -1156,13 +1156,13 @@
         <v>0.9792</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3318</v>
+        <v>0.1095</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8893</v>
+        <v>0.4799</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5575</v>
+        <v>-0.3704</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0053</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. CABAÑEROS MORALA</t>
+          <t>M. JUAN SEVILLANO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1254</v>
+        <v>-2.7845</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8781</v>
+        <v>-1.7895</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2473</v>
+        <v>-0.995</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6718</v>
+        <v>-2.8898</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1065</v>
+        <v>-2.3692</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7783</v>
+        <v>-0.5206</v>
       </c>
       <c r="J10" t="n">
-        <v>3.2863</v>
+        <v>-0.8086</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7758</v>
+        <v>-0.9443</v>
       </c>
       <c r="L10" t="n">
-        <v>2.5106</v>
+        <v>0.1357</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.6145</v>
+        <v>-2.0812</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8822</v>
+        <v>-1.4249</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.7323</v>
+        <v>-0.6563</v>
       </c>
       <c r="P10" t="n">
-        <v>-5.0921</v>
+        <v>0.3917</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.8755</v>
+        <v>-0.9792</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7834</v>
+        <v>1.3709</v>
       </c>
       <c r="S10" t="n">
-        <v>0.629</v>
+        <v>-0.2223</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7111</v>
+        <v>-0.277</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.08210000000000001</v>
+        <v>0.0547</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6659</v>
+        <v>-0.0641</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6659</v>
+        <v>-0.3394</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. JUAN SEVILLANO</t>
+          <t>P. CABAÑEROS MORALA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9925</v>
+        <v>-2.9116</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4629</v>
+        <v>-1.8781</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5296</v>
+        <v>-1.0335</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.8898</v>
+        <v>0.6718</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.3692</v>
+        <v>-0.1065</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5206</v>
+        <v>0.7783</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8086</v>
+        <v>3.2863</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9443</v>
+        <v>0.7758</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1357</v>
+        <v>2.5106</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.0812</v>
+        <v>-2.6145</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.4249</v>
+        <v>-0.8822</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6563</v>
+        <v>-1.7323</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3917</v>
+        <v>-5.0921</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9792</v>
+        <v>-5.8755</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3709</v>
+        <v>0.7834</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4303</v>
+        <v>0.8428</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9504</v>
+        <v>0.7111</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4799</v>
+        <v>0.1317</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.0641</v>
+        <v>0.6659</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3394</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="12">
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4292</v>
+        <v>-3.1322</v>
       </c>
       <c r="E12" t="n">
-        <v>8.402499999999998</v>
+        <v>8.6995</v>
       </c>
       <c r="F12" t="n">
-        <v>-11.8316</v>
+        <v>-11.8318</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.124700000000001</v>
+        <v>-4.1247</v>
       </c>
       <c r="H12" t="n">
-        <v>-6.8016</v>
+        <v>-6.801600000000001</v>
       </c>
       <c r="I12" t="n">
         <v>2.677</v>
@@ -1366,7 +1366,7 @@
         <v>19.359</v>
       </c>
       <c r="K12" t="n">
-        <v>2.010300000000001</v>
+        <v>2.0103</v>
       </c>
       <c r="L12" t="n">
         <v>17.3488</v>
@@ -1381,7 +1381,7 @@
         <v>-14.6718</v>
       </c>
       <c r="P12" t="n">
-        <v>-7.834</v>
+        <v>-7.834000000000001</v>
       </c>
       <c r="Q12" t="n">
         <v>-19.5849</v>
@@ -1390,19 +1390,19 @@
         <v>11.7507</v>
       </c>
       <c r="S12" t="n">
-        <v>2.376199999999999</v>
+        <v>2.6731</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4439</v>
+        <v>1.7409</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9321999999999997</v>
+        <v>0.9322000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>6.1531</v>
       </c>
       <c r="W12" t="n">
-        <v>7.1846</v>
+        <v>7.184600000000001</v>
       </c>
       <c r="X12" t="n">
         <v>-1.0312</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.4047</v>
+        <v>10.3187</v>
       </c>
       <c r="E13" t="n">
-        <v>10.9537</v>
+        <v>10.135</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4511</v>
+        <v>0.1838</v>
       </c>
       <c r="G13" t="n">
         <v>7.8602</v>
@@ -1468,13 +1468,13 @@
         <v>2.546</v>
       </c>
       <c r="S13" t="n">
-        <v>1.9938</v>
+        <v>0.9078000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1492</v>
+        <v>0.3305</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8446</v>
+        <v>0.5773</v>
       </c>
       <c r="V13" t="n">
         <v>1.159</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. TOMIC</t>
+          <t>A. IGLESIAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3685</v>
+        <v>2.1513</v>
       </c>
       <c r="E14" t="n">
-        <v>1.055</v>
+        <v>1.8748</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3135</v>
+        <v>0.2765</v>
       </c>
       <c r="G14" t="n">
-        <v>1.593</v>
+        <v>1.5962</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4866</v>
+        <v>1.0003</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1064</v>
+        <v>0.5958</v>
       </c>
       <c r="J14" t="n">
-        <v>2.0472</v>
+        <v>2.8576</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1429</v>
+        <v>1.0649</v>
       </c>
       <c r="L14" t="n">
-        <v>1.9043</v>
+        <v>1.7927</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4542</v>
+        <v>-1.2615</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3437</v>
+        <v>-0.0646</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-1.1969</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1751</v>
+        <v>1.9585</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1958</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3709</v>
+        <v>1.9585</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8489</v>
+        <v>-0.6798999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7963</v>
+        <v>-0.2594</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0526</v>
+        <v>-0.4205</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5507</v>
+        <v>-0.7235</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>-0.7235</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. IGLESIAS FERNANDEZ</t>
+          <t>M. TOMIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2165</v>
+        <v>1.6266</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2608</v>
+        <v>1.2597</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0443</v>
+        <v>0.3669</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5962</v>
+        <v>1.593</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0003</v>
+        <v>0.4866</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5958</v>
+        <v>1.1064</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8576</v>
+        <v>2.0472</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0649</v>
+        <v>0.1429</v>
       </c>
       <c r="L15" t="n">
-        <v>1.7927</v>
+        <v>1.9043</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2615</v>
+        <v>-0.4542</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0646</v>
+        <v>0.3437</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1969</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>1.9585</v>
+        <v>1.1751</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.1958</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9585</v>
+        <v>1.3709</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.6147</v>
+        <v>-0.5908</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8734</v>
+        <v>-0.5917</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7413</v>
+        <v>0.0009</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.7235</v>
+        <v>-0.5507</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.7235</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. SABATER MARTINEZ</t>
+          <t>D. SNYERS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3427</v>
+        <v>0.4417</v>
       </c>
       <c r="E16" t="n">
-        <v>3.892</v>
+        <v>1.2949</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.5493</v>
+        <v>-0.8531</v>
       </c>
       <c r="G16" t="n">
-        <v>0.058</v>
+        <v>1.1301</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2296</v>
+        <v>1.2766</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.1717</v>
+        <v>-0.1465</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5433</v>
+        <v>3.8748</v>
       </c>
       <c r="K16" t="n">
-        <v>3.1796</v>
+        <v>1.8849</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3637</v>
+        <v>1.99</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.4853</v>
+        <v>-2.7447</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9499</v>
+        <v>-0.6083</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.5354</v>
+        <v>-2.1364</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5668</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9792</v>
+        <v>-3.1336</v>
       </c>
       <c r="R16" t="n">
-        <v>2.546</v>
+        <v>2.1543</v>
       </c>
       <c r="S16" t="n">
-        <v>1.8746</v>
+        <v>-0.3174</v>
       </c>
       <c r="T16" t="n">
-        <v>2.0514</v>
+        <v>-0.0547</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1768</v>
+        <v>-0.2627</v>
       </c>
       <c r="V16" t="n">
-        <v>-3.1567</v>
+        <v>0.6083</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.7235</v>
+        <v>0.6083</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.4332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1035</v>
+        <v>-0.1348</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3543</v>
+        <v>0.4567</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4579</v>
+        <v>-0.5915</v>
       </c>
       <c r="G17" t="n">
         <v>-0.309</v>
@@ -1780,13 +1780,13 @@
         <v>0.5875</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1067</v>
+        <v>-0.1381</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4752</v>
+        <v>-0.3729</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3685</v>
+        <v>0.2348</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2754</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. SNYERS</t>
+          <t>P. ROQUE DO VALE CARVAHAL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2433</v>
+        <v>-0.1691</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4762</v>
+        <v>1.1155</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7195</v>
+        <v>-1.2846</v>
       </c>
       <c r="G18" t="n">
-        <v>1.1301</v>
+        <v>-0.5835</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2766</v>
+        <v>-0.1289</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1465</v>
+        <v>-0.4546</v>
       </c>
       <c r="J18" t="n">
-        <v>3.8748</v>
+        <v>0.5363</v>
       </c>
       <c r="K18" t="n">
-        <v>1.8849</v>
+        <v>-0.2008</v>
       </c>
       <c r="L18" t="n">
-        <v>1.99</v>
+        <v>0.7371</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.7447</v>
+        <v>-1.1198</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6083</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.1364</v>
+        <v>-1.1917</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9792</v>
+        <v>2.7419</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.1336</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1543</v>
+        <v>2.7419</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0025</v>
+        <v>-0.9957</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8734</v>
+        <v>-0.5223</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1291</v>
+        <v>-0.4734</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6083</v>
+        <v>-1.3318</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6083</v>
+        <v>1.1014</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.4332</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. ROQUE DO VALE CARVAHAL</t>
+          <t>G. SABATER MARTINEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.467</v>
+        <v>-0.9388</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6038</v>
+        <v>2.664</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0707</v>
+        <v>-3.6027</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5835</v>
+        <v>0.058</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1289</v>
+        <v>2.2296</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4546</v>
+        <v>-2.1717</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5363</v>
+        <v>3.5433</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2008</v>
+        <v>3.1796</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7371</v>
+        <v>0.3637</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1198</v>
+        <v>-3.4853</v>
       </c>
       <c r="N19" t="n">
-        <v>0.07190000000000001</v>
+        <v>-0.9499</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1917</v>
+        <v>-2.5354</v>
       </c>
       <c r="P19" t="n">
-        <v>2.7419</v>
+        <v>1.5668</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R19" t="n">
-        <v>2.7419</v>
+        <v>2.546</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2935</v>
+        <v>0.5931</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0339</v>
+        <v>0.8234</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2596</v>
+        <v>-0.2302</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.3318</v>
+        <v>-3.1567</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1014</v>
+        <v>-0.7235</v>
       </c>
       <c r="X19" t="n">
         <v>-2.4332</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4144</v>
+        <v>-1.6412</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3817</v>
+        <v>-1.6887</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0327</v>
+        <v>0.0475</v>
       </c>
       <c r="G20" t="n">
         <v>-0.0538</v>
@@ -2014,13 +2014,13 @@
         <v>1.5668</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1071</v>
+        <v>-0.3339</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2247</v>
+        <v>-0.0823</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3318</v>
+        <v>-0.2516</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6659</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6715</v>
+        <v>-2.4577</v>
       </c>
       <c r="E21" t="n">
         <v>-2.6945</v>
       </c>
       <c r="F21" t="n">
-        <v>0.023</v>
+        <v>0.2368</v>
       </c>
       <c r="G21" t="n">
         <v>-2.5524</v>
@@ -2092,13 +2092,13 @@
         <v>1.7626</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9026</v>
+        <v>-0.6887</v>
       </c>
       <c r="T21" t="n">
         <v>0.0465</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.949</v>
+        <v>-0.7352</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9024</v>
+        <v>-2.8444</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6198</v>
+        <v>-1.7222</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2826</v>
+        <v>-1.1222</v>
       </c>
       <c r="G22" t="n">
         <v>-2.4153</v>
@@ -2170,13 +2170,13 @@
         <v>1.9585</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2912</v>
+        <v>-0.2332</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0641</v>
+        <v>-0.0382</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3553</v>
+        <v>-0.195</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1011</v>
+        <v>-2.9232</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.068</v>
+        <v>-0.8633</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0331</v>
+        <v>-2.0599</v>
       </c>
       <c r="G23" t="n">
         <v>-2.199</v>
@@ -2248,13 +2248,13 @@
         <v>0.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0772</v>
+        <v>0.1007</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4158</v>
+        <v>-0.2111</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3386</v>
+        <v>0.3119</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2166</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>3.429199999999998</v>
+        <v>3.4291</v>
       </c>
       <c r="E24" t="n">
-        <v>11.8318</v>
+        <v>11.8319</v>
       </c>
       <c r="F24" t="n">
         <v>-8.4025</v>
       </c>
       <c r="G24" t="n">
-        <v>4.124499999999998</v>
+        <v>4.124499999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>6.801599999999997</v>
+        <v>6.801599999999999</v>
       </c>
       <c r="I24" t="n">
         <v>-2.6772</v>
@@ -2302,7 +2302,7 @@
         <v>23.4836</v>
       </c>
       <c r="K24" t="n">
-        <v>8.812000000000001</v>
+        <v>8.811999999999998</v>
       </c>
       <c r="L24" t="n">
         <v>14.6718</v>
@@ -2317,7 +2317,7 @@
         <v>-17.3489</v>
       </c>
       <c r="P24" t="n">
-        <v>7.834099999999999</v>
+        <v>7.8341</v>
       </c>
       <c r="Q24" t="n">
         <v>-11.7507</v>
@@ -2326,13 +2326,13 @@
         <v>19.5847</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.376</v>
+        <v>-2.3761</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9320999999999997</v>
+        <v>-0.9321999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.4438</v>
+        <v>-1.4437</v>
       </c>
       <c r="V24" t="n">
         <v>-6.1533</v>
@@ -2341,7 +2341,7 @@
         <v>1.0312</v>
       </c>
       <c r="X24" t="n">
-        <v>-7.184499999999999</v>
+        <v>-7.1845</v>
       </c>
     </row>
   </sheetData>
